--- a/lab_5/models/metrics/lightgbm.xlsx
+++ b/lab_5/models/metrics/lightgbm.xlsx
@@ -467,117 +467,117 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.9395</v>
+        <v>0.9362</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8293</v>
+        <v>0.8238</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1391</v>
+        <v>0.1333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.525</v>
+        <v>0.4242</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2199</v>
+        <v>0.2029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1993</v>
+        <v>0.179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2484</v>
+        <v>0.2122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.9379</v>
+        <v>0.9397</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8237</v>
+        <v>0.822</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1067</v>
+        <v>0.1321</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4571</v>
+        <v>0.5385</v>
       </c>
       <c r="E3" t="n">
-        <v>0.173</v>
+        <v>0.2121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1535</v>
+        <v>0.1926</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1989</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.9399</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8341</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1467</v>
+        <v>0.181</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5238</v>
+        <v>0.5758</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2292</v>
+        <v>0.2754</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2081</v>
+        <v>0.2536</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2549</v>
+        <v>0.3007</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9423</v>
+        <v>0.9379</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8315</v>
+        <v>0.8176</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2067</v>
+        <v>0.1333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.4667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3039</v>
+        <v>0.2074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2807</v>
+        <v>0.1853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3213</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.9379</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8199</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1192</v>
+        <v>0.1333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4737</v>
+        <v>0.6087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1905</v>
+        <v>0.2188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.17</v>
+        <v>0.2013</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2152</v>
+        <v>0.2663</v>
       </c>
     </row>
     <row r="7">
@@ -585,45 +585,45 @@
         <v>0.9395</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8277</v>
+        <v>0.8256</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1437</v>
+        <v>0.1426</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5107</v>
+        <v>0.5228</v>
       </c>
       <c r="E7" t="n">
         <v>0.2233</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2023</v>
+        <v>0.2024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2477</v>
+        <v>0.2502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0016</v>
+        <v>0.0023</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0052</v>
+        <v>0.0086</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0345</v>
+        <v>0.0192</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0415</v>
+        <v>0.0683</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0451</v>
+        <v>0.0266</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0439</v>
+        <v>0.0267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0422</v>
+        <v>0.0312</v>
       </c>
     </row>
   </sheetData>
